--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99931318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53265249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,8 +1018,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117894779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,44 +680,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99931318</v>
+        <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>99156</v>
+        <v>111556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -761,17 +753,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fyra blommande. Växer intill stigen.</t>
+          <t>Flera ex. Växer i fuktigt stråk intill stigen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,54 +800,67 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99931318</t>
+          <t>https://artportalen.se/Sighting/135848412</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53265249</v>
+        <v>99931318</v>
       </c>
       <c r="B3" t="n">
-        <v>99059</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219792</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grytholmen, Hembygdsgården, Srm</t>
+          <t>Grytholmen, södra stranden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680618</v>
+        <v>680690</v>
       </c>
       <c r="R3" t="n">
-        <v>6543443</v>
+        <v>6543195</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,17 +887,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett hundratal blommande exemplar på hävdad gräsmark runt hembygdsgårdsbyggnader.</t>
+          <t>Fyra blommande. Växer intill stigen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +906,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,22 +918,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Rolf Wahlström, Monica Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53265249</t>
+          <t>https://artportalen.se/Sighting/99931318</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117894779</v>
+        <v>53265249</v>
       </c>
       <c r="B4" t="n">
-        <v>104641</v>
+        <v>99059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,28 +941,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>219792</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Dactylorhiza sambucina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grytholmen, Hembygdsgården, Srm</t>
@@ -983,17 +998,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i den sydvända slänten.</t>
+          <t>Ett hundratal blommande exemplar på hävdad gräsmark runt hembygdsgårdsbyggnader.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1017,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1034,475 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/53265249</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135848884</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grytholmen, västra stranden, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>680589</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6543319</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Intill stigen i lövskogsområdet.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135848884</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117894779</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grytholmen, Hembygdsgården, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>680618</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6543443</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i den sydvända slänten.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/117894779</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135848748</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99304</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grytholmen, sydöstra stranden, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>680877</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6543170</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I gräsmark intilkl stigen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135848748</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135848711</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102717</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grytholmen, sydöstra stranden, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>680877</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6543170</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer utmed stigen på gräsmark.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135848711</t>
         </is>
       </c>
     </row>
@@ -1029,6 +1511,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,36 +680,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135848412</v>
+        <v>99931318</v>
       </c>
       <c r="B2" t="n">
-        <v>111556</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -753,27 +761,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>01:00</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>01:30</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera ex. Växer i fuktigt stråk intill stigen.</t>
+          <t>Fyra blommande. Växer intill stigen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,67 +798,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135848412</t>
+          <t>https://artportalen.se/Sighting/99931318</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99931318</v>
+        <v>53265249</v>
       </c>
       <c r="B3" t="n">
-        <v>99156</v>
+        <v>99059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>219792</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grytholmen, södra stranden, Srm</t>
+          <t>Grytholmen, Hembygdsgården, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680690</v>
+        <v>680618</v>
       </c>
       <c r="R3" t="n">
-        <v>6543195</v>
+        <v>6543443</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,17 +872,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fyra blommande. Växer intill stigen.</t>
+          <t>Ett hundratal blommande exemplar på hävdad gräsmark runt hembygdsgårdsbyggnader.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -918,22 +902,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Wahlström, Monica Svensson</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99931318</t>
+          <t>https://artportalen.se/Sighting/53265249</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53265249</v>
+        <v>117894779</v>
       </c>
       <c r="B4" t="n">
-        <v>99059</v>
+        <v>104641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,27 +925,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219792</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grytholmen, Hembygdsgården, Srm</t>
@@ -998,17 +983,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett hundratal blommande exemplar på hävdad gräsmark runt hembygdsgårdsbyggnader.</t>
+          <t>Rikligt i den sydvända slänten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,6 +1002,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,475 +1020,7 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53265249</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135848884</v>
-      </c>
-      <c r="B5" t="n">
-        <v>99248</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>223609</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vanlig skogsknipprot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Grytholmen, västra stranden, Srm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>680589</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6543319</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Muskö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Intill stigen i lövskogsområdet.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström, Monica Svensson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135848884</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>117894779</v>
-      </c>
-      <c r="B6" t="n">
-        <v>104641</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>224416</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ljus solvända</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Grytholmen, Hembygdsgården, Srm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>680618</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6543443</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Muskö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt i den sydvända slänten.</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/117894779</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135848748</v>
-      </c>
-      <c r="B7" t="n">
-        <v>99304</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>219874</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Grytholmen, sydöstra stranden, Srm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>680877</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6543170</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Muskö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I gräsmark intilkl stigen.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström, Monica Svensson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135848748</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>135848711</v>
-      </c>
-      <c r="B8" t="n">
-        <v>102717</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>265350</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vanligt jungfrulin</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Polygala vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Grytholmen, sydöstra stranden, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>680877</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6543170</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Muskö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer utmed stigen på gräsmark.</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström, Monica Svensson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135848711</t>
         </is>
       </c>
     </row>
@@ -1511,10 +1029,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,44 +680,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99931318</v>
+        <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>99156</v>
+        <v>111561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -761,17 +753,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fyra blommande. Växer intill stigen.</t>
+          <t>Flera ex. Växer i fuktigt stråk intill stigen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,54 +800,67 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99931318</t>
+          <t>https://artportalen.se/Sighting/135848412</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53265249</v>
+        <v>99931318</v>
       </c>
       <c r="B3" t="n">
-        <v>99059</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219792</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grytholmen, Hembygdsgården, Srm</t>
+          <t>Grytholmen, södra stranden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680618</v>
+        <v>680690</v>
       </c>
       <c r="R3" t="n">
-        <v>6543443</v>
+        <v>6543195</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,17 +887,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-05-07</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett hundratal blommande exemplar på hävdad gräsmark runt hembygdsgårdsbyggnader.</t>
+          <t>Fyra blommande. Växer intill stigen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +906,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,22 +918,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Rolf Wahlström, Monica Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53265249</t>
+          <t>https://artportalen.se/Sighting/99931318</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117894779</v>
+        <v>53265249</v>
       </c>
       <c r="B4" t="n">
-        <v>104641</v>
+        <v>99059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,28 +941,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>219792</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Dactylorhiza sambucina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grytholmen, Hembygdsgården, Srm</t>
@@ -983,17 +998,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i den sydvända slänten.</t>
+          <t>Ett hundratal blommande exemplar på hävdad gräsmark runt hembygdsgårdsbyggnader.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1017,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1034,475 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/53265249</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135848884</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99253</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grytholmen, västra stranden, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>680589</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6543319</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Intill stigen i lövskogsområdet.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135848884</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117894779</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grytholmen, Hembygdsgården, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>680618</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6543443</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i den sydvända slänten.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/117894779</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135848748</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99309</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grytholmen, sydöstra stranden, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>680877</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6543170</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I gräsmark intilkl stigen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135848748</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135848711</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102722</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grytholmen, sydöstra stranden, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>680877</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6543170</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Muskö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer utmed stigen på gräsmark.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Monica Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135848711</t>
         </is>
       </c>
     </row>
@@ -1029,6 +1511,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111561</v>
+        <v>111563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99253</v>
+        <v>99255</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102722</v>
+        <v>102724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111563</v>
+        <v>111586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99255</v>
+        <v>99272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102724</v>
+        <v>102743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102743</v>
+        <v>102745</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102745</v>
+        <v>102746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102746</v>
+        <v>102747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99275</v>
+        <v>99281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102747</v>
+        <v>102753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99337</v>
+        <v>99338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102753</v>
+        <v>102754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99282</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99338</v>
+        <v>99349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102754</v>
+        <v>102765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99349</v>
+        <v>99362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102765</v>
+        <v>102778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
